--- a/feature/add-example-for-psindiv/ig/StructureDefinition-sas-categorie-orientation.xlsx
+++ b/feature/add-example-for-psindiv/ig/StructureDefinition-sas-categorie-orientation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T16:43:23+00:00</t>
+    <t>2026-01-06T16:49:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/add-example-for-psindiv/ig/StructureDefinition-sas-categorie-orientation.xlsx
+++ b/feature/add-example-for-psindiv/ig/StructureDefinition-sas-categorie-orientation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T16:49:45+00:00</t>
+    <t>2026-01-06T17:05:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
